--- a/artfynd/A 34789-2026 artfynd.xlsx
+++ b/artfynd/A 34789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042871</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34789-2026 artfynd.xlsx
+++ b/artfynd/A 34789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042871</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34789-2026 artfynd.xlsx
+++ b/artfynd/A 34789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042871</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34789-2026 artfynd.xlsx
+++ b/artfynd/A 34789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042871</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
